--- a/submission/附件2：第三届河南省高等学校信息技术应用创新技能大赛报名表.xlsx
+++ b/submission/附件2：第三届河南省高等学校信息技术应用创新技能大赛报名表.xlsx
@@ -1339,7 +1339,9 @@
       <c r="P4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="7"/>
+      <c r="Q4" s="7">
+        <v>16691532935</v>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:18">
       <c r="A5" s="7">
